--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndvam\PycharmProjects\SRGAN_DL_PROJECT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB685591-683A-4553-9BEF-51A95C96A63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90071CCC-1675-41EF-AE2E-E365C0B81A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>Code Verification</t>
   </si>
@@ -82,6 +82,21 @@
   </si>
   <si>
     <t xml:space="preserve">Change loss weights according to loss logs </t>
+  </si>
+  <si>
+    <t>BassLine - Adverserial Loss - TVLoss</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>BassLine - Adverserial Loss</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -140,14 +155,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -446,25 +461,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1"/>
+      <c r="F1" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
+      <c r="A2" s="4"/>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -480,7 +497,7 @@
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -496,7 +513,7 @@
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
+      <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
@@ -512,7 +529,7 @@
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
@@ -528,23 +545,23 @@
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="1"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
+      <c r="A8" s="4"/>
       <c r="B8" s="1"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="1"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
+      <c r="A10" s="4"/>
       <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -569,6 +586,15 @@
       <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1">
+        <v>5</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
@@ -584,11 +610,33 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
-      <c r="B15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="1">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
-      <c r="B16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
@@ -607,7 +655,7 @@
       <c r="B20" s="1"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -624,7 +672,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
+      <c r="A22" s="4"/>
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
@@ -639,35 +687,35 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
+      <c r="A23" s="4"/>
       <c r="B23" s="1"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
+      <c r="A24" s="4"/>
       <c r="B24" s="1"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="3"/>
+      <c r="A25" s="4"/>
       <c r="B25" s="1"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="3"/>
+      <c r="A26" s="4"/>
       <c r="B26" s="1"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="3"/>
+      <c r="A27" s="4"/>
       <c r="B27" s="1"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="3"/>
+      <c r="A28" s="4"/>
       <c r="B28" s="1"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
+      <c r="A29" s="4"/>
       <c r="B29" s="1"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="3"/>
+      <c r="A30" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndvam\PycharmProjects\SRGAN_DL_PROJECT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97252\Desktop\SRGAN\SRGAN_DL_PROJECT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90071CCC-1675-41EF-AE2E-E365C0B81A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30CECCC-B968-4B66-AEF7-46F25D024AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SRGAN" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
-  <si>
-    <t>Code Verification</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>Task</t>
   </si>
@@ -97,6 +94,12 @@
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>Code Verification + Report</t>
+  </si>
+  <si>
+    <t>Verify all loss components</t>
   </si>
 </sst>
 </file>
@@ -451,39 +454,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.88671875" customWidth="1"/>
-    <col min="2" max="2" width="57.88671875" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="22.44140625" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" customWidth="1"/>
+    <col min="1" max="1" width="30.85546875" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1">
         <v>3</v>
@@ -492,14 +495,16 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1">
         <v>3</v>
@@ -508,14 +513,16 @@
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
@@ -524,14 +531,16 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
         <v>5</v>
@@ -540,36 +549,43 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1">
         <v>5</v>
@@ -578,13 +594,13 @@
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
@@ -593,25 +609,25 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="1">
         <v>5</v>
@@ -620,46 +636,46 @@
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="1">
-        <v>5</v>
-      </c>
-      <c r="D16" s="1">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
@@ -668,13 +684,13 @@
         <v>2</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1">
         <v>4</v>
@@ -683,38 +699,38 @@
         <v>2</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
     </row>
   </sheetData>
